--- a/artfynd/A 27191-2024 artfynd.xlsx
+++ b/artfynd/A 27191-2024 artfynd.xlsx
@@ -1551,7 +1551,7 @@
         <v>118348269</v>
       </c>
       <c r="B10" t="n">
-        <v>78220</v>
+        <v>78227</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1650,10 +1650,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118366218</v>
+        <v>118369083</v>
       </c>
       <c r="B11" t="n">
-        <v>97846</v>
+        <v>78136</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1662,50 +1662,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Oljonstorpet (Oljonstorpet), Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>465479</v>
+        <v>465793</v>
       </c>
       <c r="R11" t="n">
-        <v>6874388</v>
+        <v>6874387</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1761,10 +1752,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118369083</v>
+        <v>118366218</v>
       </c>
       <c r="B12" t="n">
-        <v>78129</v>
+        <v>97853</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1773,41 +1764,50 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Oljonstorpet (Oljonstorpet), Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465793</v>
+        <v>465479</v>
       </c>
       <c r="R12" t="n">
-        <v>6874387</v>
+        <v>6874388</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>

--- a/artfynd/A 27191-2024 artfynd.xlsx
+++ b/artfynd/A 27191-2024 artfynd.xlsx
@@ -1650,10 +1650,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118369083</v>
+        <v>118366218</v>
       </c>
       <c r="B11" t="n">
-        <v>78136</v>
+        <v>97853</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1662,41 +1662,50 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Oljonstorpet (Oljonstorpet), Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>465793</v>
+        <v>465479</v>
       </c>
       <c r="R11" t="n">
-        <v>6874387</v>
+        <v>6874388</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1752,10 +1761,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118366218</v>
+        <v>118369083</v>
       </c>
       <c r="B12" t="n">
-        <v>97853</v>
+        <v>78136</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1764,50 +1773,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Oljonstorpet (Oljonstorpet), Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465479</v>
+        <v>465793</v>
       </c>
       <c r="R12" t="n">
-        <v>6874388</v>
+        <v>6874387</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>

--- a/artfynd/A 27191-2024 artfynd.xlsx
+++ b/artfynd/A 27191-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1861,6 +1861,782 @@
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128190564</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79647</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Oljonstorpet, Oljonstorpet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>465694</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6874207</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128193229</v>
+      </c>
+      <c r="B14" t="n">
+        <v>78696</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>353</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Oljonstorpet, Oljonstorpet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>465790</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6874627</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128191131</v>
+      </c>
+      <c r="B15" t="n">
+        <v>78696</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>353</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Oljonstorpet, Oljonstorpet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>465783</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6874253</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128191578</v>
+      </c>
+      <c r="B16" t="n">
+        <v>78696</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>353</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Oljonstorpet, Oljonstorpet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>465869</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6874243</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128190653</v>
+      </c>
+      <c r="B17" t="n">
+        <v>92652</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Oljonstorpet, Oljonstorpet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>465736</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6874226</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128191003</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79647</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Oljonstorpet, Oljonstorpet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>465797</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6874244</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128190559</v>
+      </c>
+      <c r="B19" t="n">
+        <v>78696</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>353</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Oljonstorpet, Oljonstorpet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>465701</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6874209</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128191448</v>
+      </c>
+      <c r="B20" t="n">
+        <v>78788</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Oljonstorpet, Oljonstorpet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>465838</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6874226</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27191-2024 artfynd.xlsx
+++ b/artfynd/A 27191-2024 artfynd.xlsx
@@ -2254,7 +2254,7 @@
         <v>128190653</v>
       </c>
       <c r="B17" t="n">
-        <v>92652</v>
+        <v>92653</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 27191-2024 artfynd.xlsx
+++ b/artfynd/A 27191-2024 artfynd.xlsx
@@ -2254,7 +2254,7 @@
         <v>128190653</v>
       </c>
       <c r="B17" t="n">
-        <v>92653</v>
+        <v>92654</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 27191-2024 artfynd.xlsx
+++ b/artfynd/A 27191-2024 artfynd.xlsx
@@ -1866,7 +1866,7 @@
         <v>128190564</v>
       </c>
       <c r="B13" t="n">
-        <v>79647</v>
+        <v>79650</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>128193229</v>
       </c>
       <c r="B14" t="n">
-        <v>78696</v>
+        <v>78699</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>128191131</v>
       </c>
       <c r="B15" t="n">
-        <v>78696</v>
+        <v>78699</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>128191578</v>
       </c>
       <c r="B16" t="n">
-        <v>78696</v>
+        <v>78699</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         <v>128190653</v>
       </c>
       <c r="B17" t="n">
-        <v>92654</v>
+        <v>92662</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>128191003</v>
       </c>
       <c r="B18" t="n">
-        <v>79647</v>
+        <v>79650</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>128190559</v>
       </c>
       <c r="B19" t="n">
-        <v>78696</v>
+        <v>78699</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>128191448</v>
       </c>
       <c r="B20" t="n">
-        <v>78788</v>
+        <v>78791</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 27191-2024 artfynd.xlsx
+++ b/artfynd/A 27191-2024 artfynd.xlsx
@@ -1866,7 +1866,7 @@
         <v>128190564</v>
       </c>
       <c r="B13" t="n">
-        <v>79650</v>
+        <v>79702</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>128193229</v>
       </c>
       <c r="B14" t="n">
-        <v>78699</v>
+        <v>78749</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>128191131</v>
       </c>
       <c r="B15" t="n">
-        <v>78699</v>
+        <v>78749</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>128191578</v>
       </c>
       <c r="B16" t="n">
-        <v>78699</v>
+        <v>78749</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         <v>128190653</v>
       </c>
       <c r="B17" t="n">
-        <v>92662</v>
+        <v>92754</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>128191003</v>
       </c>
       <c r="B18" t="n">
-        <v>79650</v>
+        <v>79702</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>128190559</v>
       </c>
       <c r="B19" t="n">
-        <v>78699</v>
+        <v>78749</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>128191448</v>
       </c>
       <c r="B20" t="n">
-        <v>78791</v>
+        <v>78841</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 27191-2024 artfynd.xlsx
+++ b/artfynd/A 27191-2024 artfynd.xlsx
@@ -1866,7 +1866,7 @@
         <v>128190564</v>
       </c>
       <c r="B13" t="n">
-        <v>79702</v>
+        <v>79706</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>128193229</v>
       </c>
       <c r="B14" t="n">
-        <v>78749</v>
+        <v>78753</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>128191131</v>
       </c>
       <c r="B15" t="n">
-        <v>78749</v>
+        <v>78753</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>128191578</v>
       </c>
       <c r="B16" t="n">
-        <v>78749</v>
+        <v>78753</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         <v>128190653</v>
       </c>
       <c r="B17" t="n">
-        <v>92754</v>
+        <v>92766</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>128191003</v>
       </c>
       <c r="B18" t="n">
-        <v>79702</v>
+        <v>79706</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>128190559</v>
       </c>
       <c r="B19" t="n">
-        <v>78749</v>
+        <v>78753</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>128191448</v>
       </c>
       <c r="B20" t="n">
-        <v>78841</v>
+        <v>78845</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 27191-2024 artfynd.xlsx
+++ b/artfynd/A 27191-2024 artfynd.xlsx
@@ -1866,7 +1866,7 @@
         <v>128190564</v>
       </c>
       <c r="B13" t="n">
-        <v>79706</v>
+        <v>79708</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>128193229</v>
       </c>
       <c r="B14" t="n">
-        <v>78753</v>
+        <v>78755</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>128191131</v>
       </c>
       <c r="B15" t="n">
-        <v>78753</v>
+        <v>78755</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>128191578</v>
       </c>
       <c r="B16" t="n">
-        <v>78753</v>
+        <v>78755</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         <v>128190653</v>
       </c>
       <c r="B17" t="n">
-        <v>92766</v>
+        <v>92768</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>128191003</v>
       </c>
       <c r="B18" t="n">
-        <v>79706</v>
+        <v>79708</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>128190559</v>
       </c>
       <c r="B19" t="n">
-        <v>78753</v>
+        <v>78755</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>128191448</v>
       </c>
       <c r="B20" t="n">
-        <v>78845</v>
+        <v>78847</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 27191-2024 artfynd.xlsx
+++ b/artfynd/A 27191-2024 artfynd.xlsx
@@ -2254,7 +2254,7 @@
         <v>128190653</v>
       </c>
       <c r="B17" t="n">
-        <v>92768</v>
+        <v>92769</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 27191-2024 artfynd.xlsx
+++ b/artfynd/A 27191-2024 artfynd.xlsx
@@ -1866,7 +1866,7 @@
         <v>128190564</v>
       </c>
       <c r="B13" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>128193229</v>
       </c>
       <c r="B14" t="n">
-        <v>78755</v>
+        <v>78782</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>128191131</v>
       </c>
       <c r="B15" t="n">
-        <v>78755</v>
+        <v>78782</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>128191578</v>
       </c>
       <c r="B16" t="n">
-        <v>78755</v>
+        <v>78782</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         <v>128190653</v>
       </c>
       <c r="B17" t="n">
-        <v>92769</v>
+        <v>92796</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>128191003</v>
       </c>
       <c r="B18" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>128190559</v>
       </c>
       <c r="B19" t="n">
-        <v>78755</v>
+        <v>78782</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>128191448</v>
       </c>
       <c r="B20" t="n">
-        <v>78847</v>
+        <v>78874</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 27191-2024 artfynd.xlsx
+++ b/artfynd/A 27191-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2637,6 +2637,103 @@
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128914314</v>
+      </c>
+      <c r="B21" t="n">
+        <v>78786</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>353</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Oljonstorpet, Oljonstorpet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>465506</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6874414</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27191-2024 artfynd.xlsx
+++ b/artfynd/A 27191-2024 artfynd.xlsx
@@ -2642,7 +2642,7 @@
         <v>128914314</v>
       </c>
       <c r="B21" t="n">
-        <v>78786</v>
+        <v>78790</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 27191-2024 artfynd.xlsx
+++ b/artfynd/A 27191-2024 artfynd.xlsx
@@ -2642,7 +2642,7 @@
         <v>128914314</v>
       </c>
       <c r="B21" t="n">
-        <v>78790</v>
+        <v>78695</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 27191-2024 artfynd.xlsx
+++ b/artfynd/A 27191-2024 artfynd.xlsx
@@ -2642,7 +2642,7 @@
         <v>128914314</v>
       </c>
       <c r="B21" t="n">
-        <v>78700</v>
+        <v>78701</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 27191-2024 artfynd.xlsx
+++ b/artfynd/A 27191-2024 artfynd.xlsx
@@ -2642,7 +2642,7 @@
         <v>128914314</v>
       </c>
       <c r="B21" t="n">
-        <v>78701</v>
+        <v>78705</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 27191-2024 artfynd.xlsx
+++ b/artfynd/A 27191-2024 artfynd.xlsx
@@ -2642,7 +2642,7 @@
         <v>128914314</v>
       </c>
       <c r="B21" t="n">
-        <v>78705</v>
+        <v>78707</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 27191-2024 artfynd.xlsx
+++ b/artfynd/A 27191-2024 artfynd.xlsx
@@ -2642,7 +2642,7 @@
         <v>128914314</v>
       </c>
       <c r="B21" t="n">
-        <v>78707</v>
+        <v>78709</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 27191-2024 artfynd.xlsx
+++ b/artfynd/A 27191-2024 artfynd.xlsx
@@ -2642,7 +2642,7 @@
         <v>128914314</v>
       </c>
       <c r="B21" t="n">
-        <v>78709</v>
+        <v>78710</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 27191-2024 artfynd.xlsx
+++ b/artfynd/A 27191-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,40 +675,44 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111606560</v>
+        <v>112264157</v>
       </c>
       <c r="B2" t="n">
-        <v>90678</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4366</v>
+        <v>149</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Peck) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -716,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>465483.9886878408</v>
+        <v>465677</v>
       </c>
       <c r="R2" t="n">
-        <v>6874319.799686088</v>
+        <v>6874673</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -746,22 +750,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111606587</v>
+        <v>118369083</v>
       </c>
       <c r="B3" t="n">
-        <v>90652</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -804,35 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3100</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Oljonstorpet, Hjd</t>
+          <t>Oljonstorpet, Oljonstorpet, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465483.9886878408</v>
+        <v>465793</v>
       </c>
       <c r="R3" t="n">
-        <v>6874319.799686088</v>
+        <v>6874387</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -859,22 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,15 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111606518</v>
+        <v>128190559</v>
       </c>
       <c r="B4" t="n">
-        <v>90652</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -917,38 +890,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3100</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Oljonstorpet, Hjd</t>
+          <t>Oljonstorpet, Oljonstorpet, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465521.1460578694</v>
+        <v>465701</v>
       </c>
       <c r="R4" t="n">
-        <v>6874225.450991556</v>
+        <v>6874209</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -972,22 +944,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,15 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111606566</v>
+        <v>128191131</v>
       </c>
       <c r="B5" t="n">
-        <v>90660</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1030,38 +987,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4362</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Oljonstorpet, Hjd</t>
+          <t>Oljonstorpet, Oljonstorpet, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465483.9886878408</v>
+        <v>465783</v>
       </c>
       <c r="R5" t="n">
-        <v>6874319.799686088</v>
+        <v>6874253</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1085,22 +1041,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,63 +1073,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112264157</v>
+        <v>128191578</v>
       </c>
       <c r="B6" t="n">
-        <v>90843</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>149</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Oljonstorpet, Hjd</t>
+          <t>Oljonstorpet, Oljonstorpet, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465677</v>
+        <v>465869</v>
       </c>
       <c r="R6" t="n">
-        <v>6874673</v>
+        <v>6874243</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1207,12 +1138,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,15 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112265111</v>
+        <v>128193229</v>
       </c>
       <c r="B7" t="n">
-        <v>90849</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1255,38 +1181,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4362</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Oljonstorpet, Hjd</t>
+          <t>Oljonstorpet, Oljonstorpet, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465566</v>
+        <v>465790</v>
       </c>
       <c r="R7" t="n">
-        <v>6874278</v>
+        <v>6874627</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1310,12 +1235,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1342,15 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112423603</v>
+        <v>128914314</v>
       </c>
       <c r="B8" t="n">
-        <v>91102</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1358,38 +1278,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Oljonstorpet, Hjd</t>
+          <t>Oljonstorpet, Oljonstorpet, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>465737</v>
+        <v>465506</v>
       </c>
       <c r="R8" t="n">
-        <v>6874208</v>
+        <v>6874414</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1413,12 +1332,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-09-30</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-09-30</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1445,15 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112423248</v>
+        <v>112423603</v>
       </c>
       <c r="B9" t="n">
-        <v>77497</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1461,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>2079</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1486,10 +1400,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465680</v>
+        <v>465737</v>
       </c>
       <c r="R9" t="n">
-        <v>6874195</v>
+        <v>6874208</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1548,15 +1462,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118348269</v>
+        <v>129685765</v>
       </c>
       <c r="B10" t="n">
-        <v>78227</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1564,37 +1473,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Oljonstorpet (Oljonstorpet), Hjd</t>
+          <t>Oljonstorpet, Oljonstorpet, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465738</v>
+        <v>465544</v>
       </c>
       <c r="R10" t="n">
-        <v>6874364</v>
+        <v>6874531</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1618,12 +1527,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1650,62 +1559,49 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118366218</v>
+        <v>111606518</v>
       </c>
       <c r="B11" t="n">
-        <v>97855</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>3100</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(J.C.Schmidt) Baird</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Oljonstorpet (Oljonstorpet), Hjd</t>
+          <t>Oljonstorpet, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>465479</v>
+        <v>465522</v>
       </c>
       <c r="R11" t="n">
-        <v>6874388</v>
+        <v>6874225</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1729,12 +1625,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-07-11</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-07-11</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1761,15 +1657,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118369083</v>
+        <v>111606587</v>
       </c>
       <c r="B12" t="n">
-        <v>78138</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1777,34 +1668,35 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>3100</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Oljonstorpet (Oljonstorpet), Hjd</t>
+          <t>Oljonstorpet, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465793</v>
+        <v>465484</v>
       </c>
       <c r="R12" t="n">
-        <v>6874387</v>
+        <v>6874320</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1831,12 +1723,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-07-11</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-07-11</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1863,10 +1755,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128190564</v>
+        <v>111606566</v>
       </c>
       <c r="B13" t="n">
-        <v>79735</v>
+        <v>93191</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1874,37 +1766,38 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>4362</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Oljonstorpet, Oljonstorpet, Hjd</t>
+          <t>Oljonstorpet, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>465694</v>
+        <v>465484</v>
       </c>
       <c r="R13" t="n">
-        <v>6874207</v>
+        <v>6874320</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1928,12 +1821,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1960,10 +1853,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128193229</v>
+        <v>112265111</v>
       </c>
       <c r="B14" t="n">
-        <v>78782</v>
+        <v>93191</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1971,37 +1864,38 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>4362</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Oljonstorpet, Oljonstorpet, Hjd</t>
+          <t>Oljonstorpet, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>465790</v>
+        <v>465566</v>
       </c>
       <c r="R14" t="n">
-        <v>6874627</v>
+        <v>6874278</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2025,12 +1919,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2023-09-23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2023-09-23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2057,32 +1951,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128191131</v>
+        <v>118366891</v>
       </c>
       <c r="B15" t="n">
-        <v>78782</v>
+        <v>93201</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>4365</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2092,13 +1986,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>465783</v>
+        <v>465528</v>
       </c>
       <c r="R15" t="n">
-        <v>6874253</v>
+        <v>6874497</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2122,12 +2016,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2024-07-11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2024-07-11</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2154,10 +2048,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128191578</v>
+        <v>111606560</v>
       </c>
       <c r="B16" t="n">
-        <v>78782</v>
+        <v>93209</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2165,37 +2059,38 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>4366</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Oljonstorpet, Oljonstorpet, Hjd</t>
+          <t>Oljonstorpet, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>465869</v>
+        <v>465484</v>
       </c>
       <c r="R16" t="n">
-        <v>6874243</v>
+        <v>6874320</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2219,12 +2114,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2254,11 +2149,11 @@
         <v>128190653</v>
       </c>
       <c r="B17" t="n">
-        <v>92796</v>
+        <v>93209</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2348,48 +2243,49 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128191003</v>
+        <v>106504312</v>
       </c>
       <c r="B18" t="n">
-        <v>79735</v>
+        <v>91872</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Oljonstorpet, Oljonstorpet, Hjd</t>
+          <t>Tällberget, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>465797</v>
+        <v>465888</v>
       </c>
       <c r="R18" t="n">
-        <v>6874244</v>
+        <v>6874307</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2413,12 +2309,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2023-02-03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2023-02-03</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2445,10 +2341,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128190559</v>
+        <v>118348269</v>
       </c>
       <c r="B19" t="n">
-        <v>78782</v>
+        <v>79084</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2456,21 +2352,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2480,13 +2376,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>465701</v>
+        <v>465738</v>
       </c>
       <c r="R19" t="n">
-        <v>6874209</v>
+        <v>6874364</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2510,12 +2406,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2542,10 +2438,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128191448</v>
+        <v>129686302</v>
       </c>
       <c r="B20" t="n">
-        <v>78874</v>
+        <v>79084</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2553,21 +2449,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2577,13 +2473,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>465838</v>
+        <v>465609</v>
       </c>
       <c r="R20" t="n">
-        <v>6874226</v>
+        <v>6874640</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2607,12 +2503,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2639,10 +2535,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128914314</v>
+        <v>128190564</v>
       </c>
       <c r="B21" t="n">
-        <v>78710</v>
+        <v>79946</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2650,21 +2546,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2674,10 +2570,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>465506</v>
+        <v>465694</v>
       </c>
       <c r="R21" t="n">
-        <v>6874414</v>
+        <v>6874207</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2704,12 +2600,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2733,6 +2629,2069 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128191003</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Oljonstorpet, Oljonstorpet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>465797</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6874244</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>111024451</v>
+      </c>
+      <c r="B23" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Oljonstorpet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>465484</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6874423</v>
+      </c>
+      <c r="S23" t="n">
+        <v>20</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2023-07-24</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2023-07-24</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>111024628</v>
+      </c>
+      <c r="B24" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Oljonstorpet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>465464</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6874394</v>
+      </c>
+      <c r="S24" t="n">
+        <v>20</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2023-07-24</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2023-07-24</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>118350399</v>
+      </c>
+      <c r="B25" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Oljonstorpet, Oljonstorpet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>465845</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6874719</v>
+      </c>
+      <c r="S25" t="n">
+        <v>20</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-07-10</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-07-10</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>129685835</v>
+      </c>
+      <c r="B26" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Oljonstorpet, Oljonstorpet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>465559</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6874570</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>129685846</v>
+      </c>
+      <c r="B27" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Oljonstorpet, Oljonstorpet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>465565</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6874582</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>129685954</v>
+      </c>
+      <c r="B28" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Oljonstorpet, Oljonstorpet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>465577</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6874607</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>129686137</v>
+      </c>
+      <c r="B29" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Oljonstorpet, Oljonstorpet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>465605</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6874627</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>111024469</v>
+      </c>
+      <c r="B30" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Oljonstorpet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>465484</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6874423</v>
+      </c>
+      <c r="S30" t="n">
+        <v>20</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2023-07-24</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2023-07-24</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>111024658</v>
+      </c>
+      <c r="B31" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Oljonstorpet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>465464</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6874394</v>
+      </c>
+      <c r="S31" t="n">
+        <v>20</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2023-07-24</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2023-07-24</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>118366349</v>
+      </c>
+      <c r="B32" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Oljonstorpet, Oljonstorpet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>465486</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6874421</v>
+      </c>
+      <c r="S32" t="n">
+        <v>20</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-07-11</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-07-11</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>111606369</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57546</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>102963</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Skrattmås</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Chroicocephalus ridibundus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Oljonstorpet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>465586</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6874602</v>
+      </c>
+      <c r="S33" t="n">
+        <v>20</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2023-08-20</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2023-08-20</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>111024439</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Oljonstorpet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>465484</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6874423</v>
+      </c>
+      <c r="S34" t="n">
+        <v>20</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2023-07-24</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2023-07-24</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>118350225</v>
+      </c>
+      <c r="B35" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Oljonstorpet, Oljonstorpet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>465866</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6874719</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-07-10</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-07-10</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>118366218</v>
+      </c>
+      <c r="B36" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Oljonstorpet, Oljonstorpet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>465479</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6874388</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-07-11</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-07-11</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>118349665</v>
+      </c>
+      <c r="B37" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Oljonstorpet, Oljonstorpet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>465843</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6874564</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-07-10</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-07-10</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>111024774</v>
+      </c>
+      <c r="B38" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Oljonstorpet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>465464</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6874394</v>
+      </c>
+      <c r="S38" t="n">
+        <v>20</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2023-07-24</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2023-07-24</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>112423248</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Oljonstorpet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>465681</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6874195</v>
+      </c>
+      <c r="S39" t="n">
+        <v>20</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2023-09-30</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2023-09-30</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>128191448</v>
+      </c>
+      <c r="B40" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Oljonstorpet, Oljonstorpet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>465838</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6874226</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>129686033</v>
+      </c>
+      <c r="B41" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Oljonstorpet, Oljonstorpet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>465601</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6874633</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>129685675</v>
+      </c>
+      <c r="B42" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Oljonstorpet, Oljonstorpet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>465553</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6874530</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27191-2024 artfynd.xlsx
+++ b/artfynd/A 27191-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY42"/>
+  <dimension ref="A1:AZ42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112264157</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118369083</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128190559</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,6 +1090,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128191131</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1167,6 +1192,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128191578</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1264,6 +1294,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128193229</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1361,6 +1396,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128914314</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1459,6 +1499,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112423603</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1556,6 +1601,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129685765</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1654,6 +1704,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111606518</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1752,6 +1807,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111606587</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1850,6 +1910,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111606566</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1948,6 +2013,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112265111</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2045,6 +2115,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118366891</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2143,6 +2218,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111606560</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2240,6 +2320,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128190653</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2338,6 +2423,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106504312</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2435,6 +2525,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118348269</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2532,6 +2627,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129686302</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2629,6 +2729,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128190564</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2726,6 +2831,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128191003</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2824,6 +2934,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111024451</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2922,6 +3037,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111024628</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3019,6 +3139,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118350399</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3116,6 +3241,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129685835</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3213,6 +3343,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129685846</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3310,6 +3445,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129685954</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3407,6 +3547,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129686137</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3505,6 +3650,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111024469</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3603,6 +3753,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111024658</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3700,6 +3855,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118366349</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3798,6 +3958,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111606369</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3896,6 +4061,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111024439</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4002,6 +4172,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118350225</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4108,6 +4283,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118366218</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4205,6 +4385,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118349665</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4303,6 +4488,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111024774</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4401,6 +4591,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112423248</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4498,6 +4693,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128191448</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4595,6 +4795,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129686033</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4692,8 +4897,56 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129685675</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>